--- a/template/horaire_eleve.xlsx
+++ b/template/horaire_eleve.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/etiennerivard/notes_de_cours/support/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7C3EBE2-726B-C54C-B4F3-0611845943D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE2CD0D-2F6E-4148-B969-3F9A06BB9144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{3366A9F1-1960-6442-BD18-5D5CBE1A220F}"/>
+    <workbookView xWindow="1880" yWindow="7280" windowWidth="28040" windowHeight="17180" xr2:uid="{3366A9F1-1960-6442-BD18-5D5CBE1A220F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="ListeEtudiants_cours4202D4VI_gr00001" localSheetId="0">Sheet1!$A$1:$A$25</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="29">
   <si>
     <t>Élève</t>
   </si>
@@ -95,9 +95,6 @@
     <t>Henri L.</t>
   </si>
   <si>
-    <t>Justin L.</t>
-  </si>
-  <si>
     <t>Dany M.</t>
   </si>
   <si>
@@ -141,6 +138,12 @@
   </si>
   <si>
     <t>C205</t>
+  </si>
+  <si>
+    <t>Justin Lap.</t>
+  </si>
+  <si>
+    <t>Justin Let.</t>
   </si>
 </sst>
 </file>
@@ -530,45 +533,45 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" t="s">
         <v>24</v>
-      </c>
-      <c r="C1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1">
         <v>46132.635416666664</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1">
         <f>B2+1/24/60*15</f>
         <v>46132.645833333328</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1">
         <f t="shared" ref="B4:B7" si="0">B3+1/24/60*15</f>
         <v>46132.656249999993</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -580,19 +583,19 @@
         <v>46132.666666666657</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
         <v>46132.677083333321</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -604,42 +607,42 @@
         <v>46132.687499999985</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1">
         <v>46135.552083333336</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1">
         <f>B8+1/24/60*15</f>
         <v>46135.5625</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1">
         <f>B9+1/24/60*15</f>
         <v>46135.572916666664</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -651,7 +654,7 @@
         <v>46135.583333333328</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -663,7 +666,7 @@
         <v>46135.593749999993</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -675,18 +678,18 @@
         <v>46135.604166666657</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1">
         <v>46139.635416666664</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -698,19 +701,19 @@
         <v>46139.645833333328</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="1">
         <f>B15+1/24/60*15</f>
         <v>46139.656249999993</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -722,7 +725,7 @@
         <v>46139.666666666657</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -734,7 +737,7 @@
         <v>46139.677083333321</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -746,18 +749,18 @@
         <v>46139.687499999985</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" s="1">
         <v>46140.552083333336</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -769,19 +772,19 @@
         <v>46140.5625</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="1">
         <f>B21+1/24/60*15</f>
         <v>46140.572916666664</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -793,31 +796,31 @@
         <v>46140.583333333328</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="1">
         <f t="shared" si="1"/>
         <v>46140.593749999993</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B25" s="1">
         <f t="shared" si="1"/>
         <v>46140.604166666657</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
